--- a/MonthlyReportSummary_202502.xlsx
+++ b/MonthlyReportSummary_202502.xlsx
@@ -6,7 +6,7 @@
     <workbookView activeTab="0"/>
   </bookViews>
   <sheets>
-    <sheet name="MonthlyReportSummary_2025_03_27" r:id="rId3" sheetId="1"/>
+    <sheet name="MonthlyReportSummary_2025_04_02" r:id="rId3" sheetId="1"/>
   </sheets>
 </workbook>
 </file>
@@ -53,7 +53,7 @@
     <t>Total(kWh)</t>
   </si>
   <si>
-    <t>2025-01</t>
+    <t>2025-02</t>
   </si>
   <si>
     <t>Kecskemétiné Kiss Ildikó - Budapest</t>
@@ -286,15 +286,6 @@
       <c r="AO2" t="n" s="2">
         <v>28.0</v>
       </c>
-      <c r="AP2" t="n" s="2">
-        <v>29.0</v>
-      </c>
-      <c r="AQ2" t="n" s="2">
-        <v>30.0</v>
-      </c>
-      <c r="AR2" t="n" s="2">
-        <v>31.0</v>
-      </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="s">
@@ -420,15 +411,6 @@
       <c r="AO3" s="1" t="n">
         <v>0.0</v>
       </c>
-      <c r="AP3" s="1" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AQ3" s="1" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AR3" s="1" t="n">
-        <v>0.0</v>
-      </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="s">
@@ -453,10 +435,10 @@
         <v>19</v>
       </c>
       <c r="H4" s="1" t="n">
-        <v>31.53</v>
+        <v>61.01</v>
       </c>
       <c r="I4" s="1" t="n">
-        <v>5375.0</v>
+        <v>5455.0</v>
       </c>
       <c r="J4" s="1" t="s">
         <v>20</v>
@@ -468,100 +450,91 @@
         <v>21</v>
       </c>
       <c r="M4" s="1" t="n">
-        <v>315.3</v>
+        <v>610.1</v>
       </c>
       <c r="N4" s="1" t="n">
-        <v>1.5</v>
+        <v>23.7</v>
       </c>
       <c r="O4" s="1" t="n">
-        <v>2.8</v>
+        <v>5.5</v>
       </c>
       <c r="P4" s="1" t="n">
-        <v>10.1</v>
+        <v>10.5</v>
       </c>
       <c r="Q4" s="1" t="n">
-        <v>21.5</v>
+        <v>9.5</v>
       </c>
       <c r="R4" s="1" t="n">
-        <v>2.5</v>
+        <v>27.2</v>
       </c>
       <c r="S4" s="1" t="n">
-        <v>11.1</v>
+        <v>30.3</v>
       </c>
       <c r="T4" s="1" t="n">
-        <v>5.0</v>
+        <v>25.5</v>
       </c>
       <c r="U4" s="1" t="n">
-        <v>11.2</v>
+        <v>30.5</v>
       </c>
       <c r="V4" s="1" t="n">
-        <v>7.8</v>
+        <v>29.9</v>
       </c>
       <c r="W4" s="1" t="n">
-        <v>8.2</v>
+        <v>33.2</v>
       </c>
       <c r="X4" s="1" t="n">
-        <v>24.3</v>
+        <v>31.2</v>
       </c>
       <c r="Y4" s="1" t="n">
-        <v>16.8</v>
+        <v>9.6</v>
       </c>
       <c r="Z4" s="1" t="n">
-        <v>11.3</v>
+        <v>1.7</v>
       </c>
       <c r="AA4" s="1" t="n">
-        <v>25.5</v>
+        <v>9.8</v>
       </c>
       <c r="AB4" s="1" t="n">
-        <v>1.3</v>
+        <v>6.4</v>
       </c>
       <c r="AC4" s="1" t="n">
-        <v>2.5</v>
+        <v>10.3</v>
       </c>
       <c r="AD4" s="1" t="n">
-        <v>3.1</v>
+        <v>37.6</v>
       </c>
       <c r="AE4" s="1" t="n">
-        <v>2.5</v>
+        <v>12.1</v>
       </c>
       <c r="AF4" s="1" t="n">
-        <v>1.5</v>
+        <v>38.4</v>
       </c>
       <c r="AG4" s="1" t="n">
-        <v>1.2</v>
+        <v>37.7</v>
       </c>
       <c r="AH4" s="1" t="n">
-        <v>2.1</v>
+        <v>38.7</v>
       </c>
       <c r="AI4" s="1" t="n">
-        <v>1.8</v>
+        <v>39.1</v>
       </c>
       <c r="AJ4" s="1" t="n">
-        <v>1.7</v>
+        <v>18.3</v>
       </c>
       <c r="AK4" s="1" t="n">
-        <v>22.0</v>
+        <v>13.6</v>
       </c>
       <c r="AL4" s="1" t="n">
-        <v>9.2</v>
+        <v>26.5</v>
       </c>
       <c r="AM4" s="1" t="n">
-        <v>17.1</v>
+        <v>3.3</v>
       </c>
       <c r="AN4" s="1" t="n">
-        <v>21.0</v>
+        <v>9.1</v>
       </c>
       <c r="AO4" s="1" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AP4" s="1" t="n">
-        <v>28.2</v>
-      </c>
-      <c r="AQ4" s="1" t="n">
-        <v>28.2</v>
-      </c>
-      <c r="AR4" s="1" t="n">
-        <v>9.1</v>
+        <v>40.9</v>
       </c>
     </row>
     <row r="5">
@@ -587,10 +560,10 @@
         <v>19</v>
       </c>
       <c r="H5" s="1" t="n">
-        <v>31.53</v>
+        <v>61.01</v>
       </c>
       <c r="I5" s="1" t="n">
-        <v>9808.0</v>
+        <v>9888.0</v>
       </c>
       <c r="J5" s="1" t="s">
         <v>18</v>
@@ -602,12 +575,12 @@
         <v>18</v>
       </c>
       <c r="M5" s="1" t="n">
-        <v>315.3</v>
+        <v>610.1</v>
       </c>
     </row>
   </sheetData>
   <mergeCells>
-    <mergeCell ref="N1:AR1"/>
+    <mergeCell ref="N1:AO1"/>
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
